--- a/Pandas/exemple.xlsx
+++ b/Pandas/exemple.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Desktop\Cours\Master Cybersécurité\Projet service d'admission\Code projet\SA_Plateforme\Panda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Desktop\Cours\Master Cybersécurité\Projet service d'admission\Code projet\SA_Plateforme\Pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9178FCD3-C4BF-449C-97ED-25FC48537870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44281EC6-FB9F-4ED4-9EA2-7D4F5599CB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="2025" windowWidth="28800" windowHeight="17250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contact List" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="597">
   <si>
     <t>Prénom</t>
   </si>
@@ -893,6 +893,948 @@
   </si>
   <si>
     <t>+33622244455</t>
+  </si>
+  <si>
+    <t>Mathieu</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Bernard</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>Petit</t>
+  </si>
+  <si>
+    <t>Louis</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Durand</t>
+  </si>
+  <si>
+    <t>Dubois</t>
+  </si>
+  <si>
+    <t>Nathan</t>
+  </si>
+  <si>
+    <t>Moreau</t>
+  </si>
+  <si>
+    <t>Manon</t>
+  </si>
+  <si>
+    <t>Laurent</t>
+  </si>
+  <si>
+    <t>Jules</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Camille</t>
+  </si>
+  <si>
+    <t>Michel</t>
+  </si>
+  <si>
+    <t>Arthur</t>
+  </si>
+  <si>
+    <t>Lefebvre</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Leroy</t>
+  </si>
+  <si>
+    <t>Roux</t>
+  </si>
+  <si>
+    <t>Louise</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Bertrand</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Morel</t>
+  </si>
+  <si>
+    <t>Fournier</t>
+  </si>
+  <si>
+    <t>Lina</t>
+  </si>
+  <si>
+    <t>Girard</t>
+  </si>
+  <si>
+    <t>Chloé</t>
+  </si>
+  <si>
+    <t>Léa</t>
+  </si>
+  <si>
+    <t>Léo</t>
+  </si>
+  <si>
+    <t>Raphaël</t>
+  </si>
+  <si>
+    <t>Maël</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Bonnet</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>Lambert</t>
+  </si>
+  <si>
+    <t>Inès</t>
+  </si>
+  <si>
+    <t>Fontaine</t>
+  </si>
+  <si>
+    <t>Sacha</t>
+  </si>
+  <si>
+    <t>Rousseau</t>
+  </si>
+  <si>
+    <t>Mila</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
+  <si>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Muller</t>
+  </si>
+  <si>
+    <t>tom.muller93@testmail.fr</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>Faure</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Robin</t>
+  </si>
+  <si>
+    <t>Zoé</t>
+  </si>
+  <si>
+    <t>Masson</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Roussel</t>
+  </si>
+  <si>
+    <t>Mathis</t>
+  </si>
+  <si>
+    <t>Blanc</t>
+  </si>
+  <si>
+    <t>Clara</t>
+  </si>
+  <si>
+    <t>Gauthier</t>
+  </si>
+  <si>
+    <t>Théo</t>
+  </si>
+  <si>
+    <t>Guérin</t>
+  </si>
+  <si>
+    <t>Lilou</t>
+  </si>
+  <si>
+    <t>Morin</t>
+  </si>
+  <si>
+    <t>Timéo</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>Lucie</t>
+  </si>
+  <si>
+    <t>Perrin</t>
+  </si>
+  <si>
+    <t>Eliott</t>
+  </si>
+  <si>
+    <t>Clément</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>Axel</t>
+  </si>
+  <si>
+    <t>Jeanne</t>
+  </si>
+  <si>
+    <t>Renaud</t>
+  </si>
+  <si>
+    <t>Baptiste</t>
+  </si>
+  <si>
+    <t>Marchand</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Dumont</t>
+  </si>
+  <si>
+    <t>Antoine</t>
+  </si>
+  <si>
+    <t>Dufour</t>
+  </si>
+  <si>
+    <t>antoine.dufour38@testmail.fr</t>
+  </si>
+  <si>
+    <t>Louna</t>
+  </si>
+  <si>
+    <t>Meunier</t>
+  </si>
+  <si>
+    <t>Valentin</t>
+  </si>
+  <si>
+    <t>Brun</t>
+  </si>
+  <si>
+    <t>Ambre</t>
+  </si>
+  <si>
+    <t>Noël</t>
+  </si>
+  <si>
+    <t>Maxime</t>
+  </si>
+  <si>
+    <t>Meyer</t>
+  </si>
+  <si>
+    <t>Elsa</t>
+  </si>
+  <si>
+    <t>Chevalier</t>
+  </si>
+  <si>
+    <t>Boyer</t>
+  </si>
+  <si>
+    <t>Margaux</t>
+  </si>
+  <si>
+    <t>Garnier</t>
+  </si>
+  <si>
+    <t>Alexis</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Marine</t>
+  </si>
+  <si>
+    <t>Colin</t>
+  </si>
+  <si>
+    <t>Adrien</t>
+  </si>
+  <si>
+    <t>Legrand</t>
+  </si>
+  <si>
+    <t>Juliette</t>
+  </si>
+  <si>
+    <t>Rémy</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Schmitt</t>
+  </si>
+  <si>
+    <t>Océane</t>
+  </si>
+  <si>
+    <t>Kévin</t>
+  </si>
+  <si>
+    <t>Mélanie</t>
+  </si>
+  <si>
+    <t>Cousin</t>
+  </si>
+  <si>
+    <t>Romain</t>
+  </si>
+  <si>
+    <t>Perrot</t>
+  </si>
+  <si>
+    <t>Amandine</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>Florian</t>
+  </si>
+  <si>
+    <t>Picard</t>
+  </si>
+  <si>
+    <t>Céline</t>
+  </si>
+  <si>
+    <t>Arnaud</t>
+  </si>
+  <si>
+    <t>Damien</t>
+  </si>
+  <si>
+    <t>Roger</t>
+  </si>
+  <si>
+    <t>Audrey</t>
+  </si>
+  <si>
+    <t>Leclerc</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>Lemoine</t>
+  </si>
+  <si>
+    <t>Pauline</t>
+  </si>
+  <si>
+    <t>Georges</t>
+  </si>
+  <si>
+    <t>Sébastien</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>Caroline</t>
+  </si>
+  <si>
+    <t>Benoît</t>
+  </si>
+  <si>
+    <t>Guillaume</t>
+  </si>
+  <si>
+    <t>Rey</t>
+  </si>
+  <si>
+    <t>Hélène</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>helene.paris30@testmail.fr</t>
+  </si>
+  <si>
+    <t>Lévy</t>
+  </si>
+  <si>
+    <t>Élodie</t>
+  </si>
+  <si>
+    <t>Breton</t>
+  </si>
+  <si>
+    <t>Jérôme</t>
+  </si>
+  <si>
+    <t>Renard</t>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>Cédric</t>
+  </si>
+  <si>
+    <t>Mallet</t>
+  </si>
+  <si>
+    <t>Isabelle</t>
+  </si>
+  <si>
+    <t>Costa</t>
+  </si>
+  <si>
+    <t>Rivière</t>
+  </si>
+  <si>
+    <t>Véronique</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>Fabien</t>
+  </si>
+  <si>
+    <t>Delphine</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Christophe</t>
+  </si>
+  <si>
+    <t>Texier</t>
+  </si>
+  <si>
+    <t>Laetitia</t>
+  </si>
+  <si>
+    <t>Poirier</t>
+  </si>
+  <si>
+    <t>Stéphane</t>
+  </si>
+  <si>
+    <t>Jacquet</t>
+  </si>
+  <si>
+    <t>Émilie</t>
+  </si>
+  <si>
+    <t>Rollin</t>
+  </si>
+  <si>
+    <t>Yann</t>
+  </si>
+  <si>
+    <t>Pascal</t>
+  </si>
+  <si>
+    <t>+33656001558</t>
+  </si>
+  <si>
+    <t>+33602812045</t>
+  </si>
+  <si>
+    <t>+33641771211</t>
+  </si>
+  <si>
+    <t>+33696778128</t>
+  </si>
+  <si>
+    <t>+33778003852</t>
+  </si>
+  <si>
+    <t>+33672301983</t>
+  </si>
+  <si>
+    <t>+33760226522</t>
+  </si>
+  <si>
+    <t>+33781819217</t>
+  </si>
+  <si>
+    <t>+33629916854</t>
+  </si>
+  <si>
+    <t>+33744906725</t>
+  </si>
+  <si>
+    <t>+33643005577</t>
+  </si>
+  <si>
+    <t>+33783386918</t>
+  </si>
+  <si>
+    <t>+33647475871</t>
+  </si>
+  <si>
+    <t>+33772498831</t>
+  </si>
+  <si>
+    <t>+33740590211</t>
+  </si>
+  <si>
+    <t>+33686879079</t>
+  </si>
+  <si>
+    <t>+33794221215</t>
+  </si>
+  <si>
+    <t>+33608605221</t>
+  </si>
+  <si>
+    <t>+33641656493</t>
+  </si>
+  <si>
+    <t>+33612783949</t>
+  </si>
+  <si>
+    <t>+33654072761</t>
+  </si>
+  <si>
+    <t>+33670889497</t>
+  </si>
+  <si>
+    <t>+33620203112</t>
+  </si>
+  <si>
+    <t>+33635906688</t>
+  </si>
+  <si>
+    <t>+33781384095</t>
+  </si>
+  <si>
+    <t>+33700970970</t>
+  </si>
+  <si>
+    <t>+33792497996</t>
+  </si>
+  <si>
+    <t>+33714568274</t>
+  </si>
+  <si>
+    <t>+33612310136</t>
+  </si>
+  <si>
+    <t>+33622553194</t>
+  </si>
+  <si>
+    <t>+33707721195</t>
+  </si>
+  <si>
+    <t>+33750049874</t>
+  </si>
+  <si>
+    <t>+33722617828</t>
+  </si>
+  <si>
+    <t>+33611755828</t>
+  </si>
+  <si>
+    <t>+33737927161</t>
+  </si>
+  <si>
+    <t>+33726758887</t>
+  </si>
+  <si>
+    <t>+33756674072</t>
+  </si>
+  <si>
+    <t>+33723986457</t>
+  </si>
+  <si>
+    <t>+33713395842</t>
+  </si>
+  <si>
+    <t>+33666625168</t>
+  </si>
+  <si>
+    <t>+33744888973</t>
+  </si>
+  <si>
+    <t>+33766417761</t>
+  </si>
+  <si>
+    <t>+33720108247</t>
+  </si>
+  <si>
+    <t>+33747108510</t>
+  </si>
+  <si>
+    <t>+33780723518</t>
+  </si>
+  <si>
+    <t>+33669465862</t>
+  </si>
+  <si>
+    <t>+33649543824</t>
+  </si>
+  <si>
+    <t>+33704012674</t>
+  </si>
+  <si>
+    <t>+33798170109</t>
+  </si>
+  <si>
+    <t>+33730696229</t>
+  </si>
+  <si>
+    <t>+33667688448</t>
+  </si>
+  <si>
+    <t>+33715056519</t>
+  </si>
+  <si>
+    <t>+33739449515</t>
+  </si>
+  <si>
+    <t>+33617303597</t>
+  </si>
+  <si>
+    <t>+33710368623</t>
+  </si>
+  <si>
+    <t>+33637085398</t>
+  </si>
+  <si>
+    <t>+33627428090</t>
+  </si>
+  <si>
+    <t>+33638497884</t>
+  </si>
+  <si>
+    <t>+33611123495</t>
+  </si>
+  <si>
+    <t>+336232109111</t>
+  </si>
+  <si>
+    <t>+33991193283</t>
+  </si>
+  <si>
+    <t>lucas.martin75@yahoo.com</t>
+  </si>
+  <si>
+    <t>hugo.thomas81@orange.fr</t>
+  </si>
+  <si>
+    <t>louis.robert10@sfr.fr</t>
+  </si>
+  <si>
+    <t>jade.petit76@sfr.fr</t>
+  </si>
+  <si>
+    <t>chloe.richard44@free.frr</t>
+  </si>
+  <si>
+    <t>leo.roux43@wanadoo.fr</t>
+  </si>
+  <si>
+    <t>arthur.lefebvre11@icloud.com</t>
+  </si>
+  <si>
+    <t>manon.laurent82@icloud.com</t>
+  </si>
+  <si>
+    <t>noah.andre31@icloud.com</t>
+  </si>
+  <si>
+    <t>raphael.bertrand21@icloud.com</t>
+  </si>
+  <si>
+    <t>mael.fournier80@icloud.com</t>
+  </si>
+  <si>
+    <t>eva.morel68@icloud.com</t>
+  </si>
+  <si>
+    <t>adam.robin21@hotmail.com</t>
+  </si>
+  <si>
+    <t>julia.faure90@hotmail.com</t>
+  </si>
+  <si>
+    <t>sacha.rousseau5@hotmail.com</t>
+  </si>
+  <si>
+    <t>ines.fontaine45@hotmail.com</t>
+  </si>
+  <si>
+    <t>lina.girard34@hotmail.com</t>
+  </si>
+  <si>
+    <t>stephane.jacquet56@gmail.com</t>
+  </si>
+  <si>
+    <t>laetitia.poirier55@gmail.com</t>
+  </si>
+  <si>
+    <t>christophe.texier93@gmail.com</t>
+  </si>
+  <si>
+    <t>delphine.milan68@gmail.fr</t>
+  </si>
+  <si>
+    <t>caroline.benoit69@ggmail.com</t>
+  </si>
+  <si>
+    <t>guillaume.rey15@gmail.com</t>
+  </si>
+  <si>
+    <t>melanie.cousin42@gmail.com</t>
+  </si>
+  <si>
+    <t>benjamin.schmitt93@gmail.com</t>
+  </si>
+  <si>
+    <t>amandine.navarro89@gmail.com</t>
+  </si>
+  <si>
+    <t>kevin.paul27@gmail.com</t>
+  </si>
+  <si>
+    <t>juliette.remy59@gmail.com</t>
+  </si>
+  <si>
+    <t>marine.colin83@gmail.com</t>
+  </si>
+  <si>
+    <t>julien.lemoine91@gmail.com</t>
+  </si>
+  <si>
+    <t>sebastien.martinez24@gmail.com</t>
+  </si>
+  <si>
+    <t>pauline.georges39@gmaiil.com</t>
+  </si>
+  <si>
+    <t>elodie.breton44@gmail.com</t>
+  </si>
+  <si>
+    <t>sophie.charles78@gmail.com</t>
+  </si>
+  <si>
+    <t>cedric.mallet89@gmail.com</t>
+  </si>
+  <si>
+    <t>veronique.jean17@gmail.com</t>
+  </si>
+  <si>
+    <t>fabien.guillaume30@gmail.com</t>
+  </si>
+  <si>
+    <t>damien.roger90@gmail.com</t>
+  </si>
+  <si>
+    <t>rose.dumont7@gmail.com</t>
+  </si>
+  <si>
+    <t>baptiste.marchand12@gmail.com</t>
+  </si>
+  <si>
+    <t>jeanne.renaud37@gmail.com</t>
+  </si>
+  <si>
+    <t>axel.mathieu86@gmail.com</t>
+  </si>
+  <si>
+    <t>eliott.clement18@gmail.com</t>
+  </si>
+  <si>
+    <t>clement.boyer81@gmail.com</t>
+  </si>
+  <si>
+    <t>elsa.chevalier42@free.fr</t>
+  </si>
+  <si>
+    <t>valentin.brun73@free.fr</t>
+  </si>
+  <si>
+    <t>lilou.morin6@free.fr</t>
+  </si>
+  <si>
+    <t>theo.guerin12@free.fr</t>
+  </si>
+  <si>
+    <t>clara.gauthier6@free.fr</t>
+  </si>
+  <si>
+    <t>mathis.blanc51@free.fr</t>
+  </si>
+  <si>
+    <t>nina.roussel97@outlook.com</t>
+  </si>
+  <si>
+    <t>paul.henry79@outlook.com</t>
+  </si>
+  <si>
+    <t>zoe.masson69@outlook.com</t>
+  </si>
+  <si>
+    <t>lea.dubois59@outloook.com</t>
+  </si>
+  <si>
+    <t>laurent.riviere98@iicloud.com</t>
+  </si>
+  <si>
+    <t>isabelle.costa91@icloud.com</t>
+  </si>
+  <si>
+    <t>jerome.renard43@icloud.fr</t>
+  </si>
+  <si>
+    <t>nicolas.levy42@icloud.com</t>
+  </si>
+  <si>
+    <t>yann.pascal50@yahoo.com</t>
+  </si>
+  <si>
+    <t>emilie.rollin54yahoo.com</t>
+  </si>
+  <si>
+    <t>celine.arnaud41@yahoo.co</t>
+  </si>
+  <si>
+    <t>oceane.adam49@yahoo.com</t>
+  </si>
+  <si>
+    <t>maxime.meyer38@yahoo.com</t>
+  </si>
+  <si>
+    <t>ambre.noel61@yahoo.com</t>
+  </si>
+  <si>
+    <t>louna.meunier99@yahoo.com</t>
+  </si>
+  <si>
+    <t>louise.david32@wanadoo.fr</t>
+  </si>
+  <si>
+    <t>camille.michel61@wanadoo.fr</t>
+  </si>
+  <si>
+    <t>sarah.leroy77@wanadoo.fr</t>
+  </si>
+  <si>
+    <t>nathan.moreau14@wanadoo.fr</t>
+  </si>
+  <si>
+    <t>gabriel.durand17@mail.com</t>
+  </si>
+  <si>
+    <t>adrien.legrand94@orange.fr</t>
+  </si>
+  <si>
+    <t>romain.perrot14@orange.com</t>
+  </si>
+  <si>
+    <t>florian.picard19@orange.fr</t>
+  </si>
+  <si>
+    <t>audrey.leclerc85@orange.fr</t>
+  </si>
+  <si>
+    <t>ethan.lambert75@orange.fr</t>
+  </si>
+  <si>
+    <t>jules.simon10@orange</t>
+  </si>
+  <si>
+    <t>emma.bernard70@orange.fr</t>
+  </si>
+  <si>
+    <t>+3364811105</t>
+  </si>
+  <si>
+    <t>+337873660274</t>
+  </si>
+  <si>
+    <t>+337359436092</t>
+  </si>
+  <si>
+    <t>+3365057595</t>
+  </si>
+  <si>
+    <t>+337812346</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1896,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -967,6 +1909,8 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1524,7 +2468,18 @@
       </c>
     </row>
     <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="5"/>
+      <c r="A4" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>454</v>
+      </c>
       <c r="E4" s="4">
         <v>95520</v>
       </c>
@@ -1569,7 +2524,18 @@
       </c>
     </row>
     <row r="5" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="5"/>
+      <c r="A5" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>455</v>
+      </c>
       <c r="E5" s="4">
         <v>95610</v>
       </c>
@@ -1608,6 +2574,15 @@
       </c>
     </row>
     <row r="6" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>516</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="4">
         <v>95280</v>
@@ -1653,7 +2628,18 @@
       </c>
     </row>
     <row r="7" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>592</v>
+      </c>
       <c r="E7" s="4">
         <v>78700</v>
       </c>
@@ -1689,7 +2675,18 @@
       </c>
     </row>
     <row r="8" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="5"/>
+      <c r="A8" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>456</v>
+      </c>
       <c r="E8" s="4">
         <v>95100</v>
       </c>
@@ -1731,7 +2728,18 @@
       </c>
     </row>
     <row r="9" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="5"/>
+      <c r="A9" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>514</v>
+      </c>
       <c r="E9" s="4">
         <v>95280</v>
       </c>
@@ -1758,7 +2766,18 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="5"/>
+      <c r="A10" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>513</v>
+      </c>
       <c r="E10" s="4">
         <v>95450</v>
       </c>
@@ -1782,7 +2801,18 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="5"/>
+      <c r="A11" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>493</v>
+      </c>
       <c r="E11" s="4">
         <v>95520</v>
       </c>
@@ -1827,7 +2857,18 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="5"/>
+      <c r="A12" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>492</v>
+      </c>
       <c r="E12" s="4">
         <v>95180</v>
       </c>
@@ -1872,7 +2913,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="5"/>
+      <c r="A13" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="D13" s="5">
+        <v>761401042</v>
+      </c>
       <c r="E13" s="4">
         <v>78130</v>
       </c>
@@ -1914,7 +2966,18 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="5"/>
+      <c r="A14" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>507</v>
+      </c>
       <c r="E14" s="4">
         <v>95800</v>
       </c>
@@ -1941,7 +3004,18 @@
       </c>
     </row>
     <row r="15" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="5"/>
+      <c r="A15" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>457</v>
+      </c>
       <c r="E15" s="4">
         <v>95000</v>
       </c>
@@ -1974,7 +3048,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="5"/>
+      <c r="A16" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>458</v>
+      </c>
       <c r="E16" s="4">
         <v>95820</v>
       </c>
@@ -2004,7 +3089,18 @@
       </c>
     </row>
     <row r="17" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="5"/>
+      <c r="A17" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>512</v>
+      </c>
       <c r="E17" s="4">
         <v>95620</v>
       </c>
@@ -2049,7 +3145,18 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="5"/>
+      <c r="A18" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>459</v>
+      </c>
       <c r="E18" s="4">
         <v>34070</v>
       </c>
@@ -2076,7 +3183,18 @@
       </c>
     </row>
     <row r="19" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="5"/>
+      <c r="A19" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>494</v>
+      </c>
       <c r="E19" s="4">
         <v>95430</v>
       </c>
@@ -2103,6 +3221,15 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4">
         <v>95800</v>
@@ -2121,7 +3248,18 @@
       </c>
     </row>
     <row r="21" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="5"/>
+      <c r="A21" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>506</v>
+      </c>
       <c r="E21" s="4">
         <v>95610</v>
       </c>
@@ -2163,7 +3301,18 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="5"/>
+      <c r="A22" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>505</v>
+      </c>
       <c r="E22" s="4">
         <v>95620</v>
       </c>
@@ -2190,7 +3339,18 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="5"/>
+      <c r="A23" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>504</v>
+      </c>
       <c r="E23" s="4">
         <v>95000</v>
       </c>
@@ -2220,7 +3380,18 @@
       </c>
     </row>
     <row r="24" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="5"/>
+      <c r="A24" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>503</v>
+      </c>
       <c r="E24" s="4">
         <v>95300</v>
       </c>
@@ -2247,7 +3418,15 @@
       </c>
     </row>
     <row r="25" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="5"/>
+      <c r="A25" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>593</v>
+      </c>
       <c r="E25" s="4">
         <v>95550</v>
       </c>
@@ -2295,7 +3474,18 @@
       </c>
     </row>
     <row r="26" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="5"/>
+      <c r="A26" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>502</v>
+      </c>
       <c r="E26" s="4">
         <v>78400</v>
       </c>
@@ -2322,10 +3512,18 @@
       </c>
     </row>
     <row r="27" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27" s="3"/>
+      <c r="A27" t="s">
+        <v>330</v>
+      </c>
+      <c r="B27" t="s">
+        <v>331</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>594</v>
+      </c>
       <c r="E27">
         <v>95250</v>
       </c>
@@ -2367,9 +3565,15 @@
       <c r="AA27"/>
     </row>
     <row r="28" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>529</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28">
         <v>95420</v>
@@ -2412,10 +3616,16 @@
       <c r="AA28"/>
     </row>
     <row r="29" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29"/>
+      <c r="A29" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" t="s">
+        <v>335</v>
+      </c>
       <c r="C29"/>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>732622480</v>
+      </c>
       <c r="E29">
         <v>95320</v>
       </c>
@@ -2457,10 +3667,18 @@
       <c r="AA29"/>
     </row>
     <row r="30" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30" s="3"/>
+      <c r="A30" t="s">
+        <v>336</v>
+      </c>
+      <c r="B30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>511</v>
+      </c>
       <c r="E30">
         <v>95290</v>
       </c>
@@ -2502,10 +3720,18 @@
       <c r="AA30"/>
     </row>
     <row r="31" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31" s="3"/>
+      <c r="A31" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s">
+        <v>340</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>500</v>
+      </c>
       <c r="E31">
         <v>95450</v>
       </c>
@@ -2547,6 +3773,15 @@
       <c r="AA31"/>
     </row>
     <row r="32" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>527</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4">
         <v>60100</v>
@@ -2591,8 +3826,19 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="5"/>
+    <row r="33" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="E33" s="4">
         <v>95280</v>
       </c>
@@ -2624,8 +3870,19 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="5"/>
+    <row r="34" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>498</v>
+      </c>
       <c r="E34" s="4">
         <v>95160</v>
       </c>
@@ -2654,8 +3911,19 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D35" s="5"/>
+    <row r="35" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>501</v>
+      </c>
       <c r="G35" s="4" t="s">
         <v>31</v>
       </c>
@@ -2687,7 +3955,16 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>564</v>
+      </c>
       <c r="D36" s="5"/>
       <c r="E36" s="4">
         <v>78700</v>
@@ -2726,7 +4003,16 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>563</v>
+      </c>
       <c r="D37" s="5"/>
       <c r="E37" s="4">
         <v>95220</v>
@@ -2771,8 +4057,19 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="5"/>
+    <row r="38" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="E38" s="4">
         <v>95520</v>
       </c>
@@ -2813,8 +4110,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="5"/>
+    <row r="39" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>496</v>
+      </c>
       <c r="E39" s="4">
         <v>78700</v>
       </c>
@@ -2852,8 +4160,16 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="5"/>
+    <row r="40" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>497</v>
+      </c>
       <c r="E40" s="4">
         <v>95190</v>
       </c>
@@ -2885,8 +4201,16 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="5"/>
+    <row r="41" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D41" s="5">
+        <v>761121481</v>
+      </c>
       <c r="G41" s="4" t="s">
         <v>31</v>
       </c>
@@ -2918,8 +4242,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
+    <row r="42" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>508</v>
+      </c>
       <c r="E42" s="4">
         <v>95310</v>
       </c>
@@ -2969,8 +4304,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="5"/>
+    <row r="43" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>491</v>
+      </c>
       <c r="E43" s="4">
         <v>95660</v>
       </c>
@@ -3011,8 +4354,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="5"/>
+    <row r="44" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>510</v>
+      </c>
       <c r="G44" s="4" t="s">
         <v>31</v>
       </c>
@@ -3047,8 +4401,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="5"/>
+    <row r="45" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D45" s="5">
+        <v>775577226</v>
+      </c>
       <c r="E45" s="4">
         <v>95660</v>
       </c>
@@ -3098,8 +4463,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D46" s="5"/>
+    <row r="46" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>509</v>
+      </c>
       <c r="E46" s="4">
         <v>95420</v>
       </c>
@@ -3143,8 +4519,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="5"/>
+    <row r="47" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D47" s="5">
+        <v>673919128</v>
+      </c>
       <c r="E47" s="4">
         <v>95000</v>
       </c>
@@ -3191,8 +4578,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="4:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="5"/>
+    <row r="48" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>490</v>
+      </c>
       <c r="E48" s="4">
         <v>95300</v>
       </c>
@@ -3234,6 +4632,15 @@
       </c>
     </row>
     <row r="49" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>579</v>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="4">
         <v>95130</v>
@@ -3279,7 +4686,18 @@
       </c>
     </row>
     <row r="50" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="5"/>
+      <c r="A50" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="D50" s="5">
+        <v>687552513</v>
+      </c>
       <c r="E50" s="4">
         <v>95300</v>
       </c>
@@ -3324,7 +4742,18 @@
       </c>
     </row>
     <row r="51" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="5"/>
+      <c r="A51" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>489</v>
+      </c>
       <c r="E51" s="4">
         <v>95520</v>
       </c>
@@ -3369,7 +4798,18 @@
       </c>
     </row>
     <row r="52" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D52" s="5"/>
+      <c r="A52" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>480</v>
+      </c>
       <c r="E52" s="4">
         <v>95100</v>
       </c>
@@ -3414,7 +4854,18 @@
       </c>
     </row>
     <row r="53" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="5"/>
+      <c r="A53" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>481</v>
+      </c>
       <c r="E53" s="4">
         <v>95800</v>
       </c>
@@ -3456,7 +4907,18 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="5"/>
+      <c r="A54" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>482</v>
+      </c>
       <c r="E54" s="4">
         <v>95110</v>
       </c>
@@ -3498,7 +4960,15 @@
       </c>
     </row>
     <row r="55" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D55" s="5"/>
+      <c r="A55" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>595</v>
+      </c>
       <c r="E55" s="4">
         <v>60530</v>
       </c>
@@ -3546,7 +5016,15 @@
       </c>
     </row>
     <row r="56" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D56" s="5"/>
+      <c r="A56" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>483</v>
+      </c>
       <c r="E56" s="4">
         <v>95280</v>
       </c>
@@ -3591,7 +5069,18 @@
       </c>
     </row>
     <row r="57" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="5"/>
+      <c r="A57" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="E57" s="4">
         <v>95520</v>
       </c>
@@ -3633,7 +5122,18 @@
       </c>
     </row>
     <row r="58" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D58" s="5"/>
+      <c r="A58" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="E58" s="4">
         <v>95180</v>
       </c>
@@ -3666,7 +5166,18 @@
       </c>
     </row>
     <row r="59" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="5"/>
+      <c r="A59" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>486</v>
+      </c>
       <c r="G59" s="4" t="s">
         <v>51</v>
       </c>
@@ -3699,10 +5210,18 @@
       </c>
     </row>
     <row r="60" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60" s="3"/>
+      <c r="A60" t="s">
+        <v>396</v>
+      </c>
+      <c r="B60" t="s">
+        <v>397</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>487</v>
+      </c>
       <c r="E60">
         <v>95280</v>
       </c>
@@ -3754,7 +5273,18 @@
       <c r="AA60"/>
     </row>
     <row r="61" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="5"/>
+      <c r="A61" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>488</v>
+      </c>
       <c r="E61" s="4">
         <v>95800</v>
       </c>
@@ -3799,7 +5329,18 @@
       </c>
     </row>
     <row r="62" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D62" s="5"/>
+      <c r="A62" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="D62" s="5">
+        <v>776624258</v>
+      </c>
       <c r="Q62" s="4" t="s">
         <v>35</v>
       </c>
@@ -3829,7 +5370,16 @@
       </c>
     </row>
     <row r="63" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="5"/>
+      <c r="A63" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="D63" s="7"/>
       <c r="E63" s="4">
         <v>95000</v>
       </c>
@@ -3871,7 +5421,16 @@
       </c>
     </row>
     <row r="64" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D64" s="5"/>
+      <c r="A64" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="D64" s="7"/>
       <c r="E64" s="4">
         <v>95310</v>
       </c>
@@ -3910,7 +5469,18 @@
       </c>
     </row>
     <row r="65" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="5"/>
+      <c r="A65" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>479</v>
+      </c>
       <c r="E65" s="4">
         <v>95540</v>
       </c>
@@ -3955,7 +5525,18 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="5"/>
+      <c r="A66" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>468</v>
+      </c>
       <c r="E66" s="4">
         <v>95450</v>
       </c>
@@ -4000,7 +5581,18 @@
       </c>
     </row>
     <row r="67" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="5"/>
+      <c r="A67" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>596</v>
+      </c>
       <c r="Q67" s="4" t="s">
         <v>35</v>
       </c>
@@ -4027,7 +5619,18 @@
       </c>
     </row>
     <row r="68" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D68" s="5"/>
+      <c r="A68" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>469</v>
+      </c>
       <c r="E68" s="4">
         <v>95150</v>
       </c>
@@ -4072,7 +5675,18 @@
       </c>
     </row>
     <row r="69" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="5"/>
+      <c r="A69" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>470</v>
+      </c>
       <c r="E69" s="4">
         <v>78700</v>
       </c>
@@ -4114,7 +5728,18 @@
       </c>
     </row>
     <row r="70" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="5"/>
+      <c r="A70" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>471</v>
+      </c>
       <c r="G70" s="4" t="s">
         <v>31</v>
       </c>
@@ -4144,7 +5769,18 @@
       </c>
     </row>
     <row r="71" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="5"/>
+      <c r="A71" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>472</v>
+      </c>
       <c r="E71" s="4">
         <v>95540</v>
       </c>
@@ -4186,7 +5822,18 @@
       </c>
     </row>
     <row r="72" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="5"/>
+      <c r="A72" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D72" s="5">
+        <v>710139504</v>
+      </c>
       <c r="E72" s="4">
         <v>95540</v>
       </c>
@@ -4225,10 +5872,18 @@
       </c>
     </row>
     <row r="73" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-      <c r="C73"/>
-      <c r="D73" s="3"/>
+      <c r="A73" t="s">
+        <v>420</v>
+      </c>
+      <c r="B73" t="s">
+        <v>421</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="E73">
         <v>60119</v>
       </c>
@@ -4280,7 +5935,18 @@
       </c>
     </row>
     <row r="74" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="5"/>
+      <c r="A74" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>475</v>
+      </c>
       <c r="E74" s="4">
         <v>95450</v>
       </c>
@@ -4313,7 +5979,18 @@
       </c>
     </row>
     <row r="75" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="5"/>
+      <c r="A75" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>474</v>
+      </c>
       <c r="E75" s="4">
         <v>95550</v>
       </c>
@@ -4349,7 +6026,18 @@
       </c>
     </row>
     <row r="76" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="5"/>
+      <c r="A76" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>476</v>
+      </c>
       <c r="G76" s="4" t="s">
         <v>31</v>
       </c>
@@ -4370,7 +6058,18 @@
       </c>
     </row>
     <row r="77" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D77" s="5"/>
+      <c r="A77" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="D77" s="5">
+        <v>748068506</v>
+      </c>
       <c r="E77" s="4">
         <v>95000</v>
       </c>
@@ -4406,7 +6105,18 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D78" s="5"/>
+      <c r="A78" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>477</v>
+      </c>
       <c r="E78" s="4">
         <v>78700</v>
       </c>
@@ -4436,7 +6146,18 @@
       </c>
     </row>
     <row r="79" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D79" s="5"/>
+      <c r="A79" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>478</v>
+      </c>
       <c r="E79" s="4">
         <v>95320</v>
       </c>
@@ -4469,7 +6190,18 @@
       </c>
     </row>
     <row r="80" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="5"/>
+      <c r="A80" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>462</v>
+      </c>
       <c r="E80" s="4">
         <v>95000</v>
       </c>
@@ -4493,7 +6225,18 @@
       </c>
     </row>
     <row r="81" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D81" s="5"/>
+      <c r="A81" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>463</v>
+      </c>
       <c r="E81" s="4">
         <v>27830</v>
       </c>
@@ -4532,7 +6275,18 @@
       </c>
     </row>
     <row r="82" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="5"/>
+      <c r="A82" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>464</v>
+      </c>
       <c r="E82" s="4">
         <v>91270</v>
       </c>
@@ -4571,7 +6325,18 @@
       </c>
     </row>
     <row r="83" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="5"/>
+      <c r="A83" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>465</v>
+      </c>
       <c r="E83" s="4">
         <v>60730</v>
       </c>
@@ -4610,10 +6375,18 @@
       </c>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="5"/>
+      <c r="A84" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>466</v>
+      </c>
       <c r="E84" s="4">
         <v>95550</v>
       </c>
@@ -4663,10 +6436,18 @@
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="5"/>
+      <c r="A85" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>461</v>
+      </c>
       <c r="E85" s="4">
         <v>95000</v>
       </c>
@@ -4716,10 +6497,18 @@
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="5"/>
+      <c r="A86" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D86" s="5">
+        <v>628395295</v>
+      </c>
       <c r="E86" s="4">
         <v>95690</v>
       </c>
@@ -4771,10 +6560,18 @@
       </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5"/>
+      <c r="A87" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>460</v>
+      </c>
       <c r="E87" s="4">
         <v>95450</v>
       </c>
@@ -4824,10 +6621,18 @@
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="5"/>
+      <c r="A88" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="D88" s="5">
+        <v>781720294</v>
+      </c>
       <c r="E88" s="4">
         <v>95000</v>
       </c>
@@ -4871,10 +6676,18 @@
       <c r="AA88" s="4"/>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="5"/>
+      <c r="A89" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>467</v>
+      </c>
       <c r="E89" s="4">
         <v>95800</v>
       </c>
@@ -4916,10 +6729,18 @@
       <c r="AA89" s="4"/>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="5"/>
+      <c r="A90" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="D90" s="5">
+        <v>744112039</v>
+      </c>
       <c r="E90" s="4">
         <v>95800</v>
       </c>
@@ -4969,6 +6790,82 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{FE62AE07-976C-461D-BCBF-52EDF056E9A8}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{B79C6F41-9EC6-4FC3-AFE0-14341814FF6F}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{B3C46BB3-018E-4561-965C-A6A1354FE911}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{F82E5057-B32A-47A7-8F2D-D39810C7211C}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{50ABBC78-4ACA-4835-9F1B-E6FE71491A6A}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{9F8FD0AB-8DB0-4763-9924-7B3064E865EF}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{E48E46EC-C3EE-43DD-9DB2-7E2421E4A1FE}"/>
+    <hyperlink ref="C18" r:id="rId8" xr:uid="{EFBC69E2-FDEC-4BBF-8DBF-DD19279044A8}"/>
+    <hyperlink ref="C16" r:id="rId9" xr:uid="{447AB505-0B2D-4298-94A2-0951D4BB5C68}"/>
+    <hyperlink ref="C13" r:id="rId10" xr:uid="{248D8A91-1069-42F6-B3B4-E2627BE26A9A}"/>
+    <hyperlink ref="C24" r:id="rId11" xr:uid="{FE7967C1-60B6-413D-9212-CF50F0CD4180}"/>
+    <hyperlink ref="C20" r:id="rId12" xr:uid="{423A066D-0019-43D5-BE19-28FBA592D327}"/>
+    <hyperlink ref="C22" r:id="rId13" xr:uid="{21452F87-757E-4930-A449-1EA39F028BC0}"/>
+    <hyperlink ref="C21" r:id="rId14" xr:uid="{462FF9B4-CB07-4188-BA91-4415656C675C}"/>
+    <hyperlink ref="C32" r:id="rId15" xr:uid="{6AB68F42-B149-4BA4-A70C-F96A569960F2}"/>
+    <hyperlink ref="C31" r:id="rId16" xr:uid="{383B1FB9-6229-46EE-9D37-52EDFE403692}"/>
+    <hyperlink ref="C28" r:id="rId17" xr:uid="{A8590AD5-5951-49E1-800E-38E27DDA8BBF}"/>
+    <hyperlink ref="C27" r:id="rId18" xr:uid="{E23215F5-59A4-43C2-BDE1-D969E707E92B}"/>
+    <hyperlink ref="C23" r:id="rId19" xr:uid="{82CC73B0-E99F-4E4C-9025-DB5E1AF5EAB3}"/>
+    <hyperlink ref="C88" r:id="rId20" xr:uid="{061F79AE-67E9-4A39-9E90-B7CE1415CD48}"/>
+    <hyperlink ref="C87" r:id="rId21" xr:uid="{1A882DD9-DFF4-49DB-B777-93F6D14B847B}"/>
+    <hyperlink ref="C86" r:id="rId22" xr:uid="{D8AF7CEF-C3B1-4A55-8EF5-DE73C33F5B35}"/>
+    <hyperlink ref="C85" r:id="rId23" xr:uid="{9F6393E0-2EEA-4947-9879-BD7519A0C2FA}"/>
+    <hyperlink ref="C73" r:id="rId24" xr:uid="{7A3B08AA-43A2-48BB-A881-D3C366F68E43}"/>
+    <hyperlink ref="C74" r:id="rId25" xr:uid="{3F9F721D-0E93-48A9-84F8-B2FDEA283434}"/>
+    <hyperlink ref="C63" r:id="rId26" xr:uid="{BD98115A-7031-4234-9CD2-A9737786C0AC}"/>
+    <hyperlink ref="C60" r:id="rId27" xr:uid="{FEAEAEB1-8380-4E21-9664-E13F8F231999}"/>
+    <hyperlink ref="C65" r:id="rId28" xr:uid="{885F6F41-6CD5-4F85-8FBB-FB3ADB94BBF9}"/>
+    <hyperlink ref="C62" r:id="rId29" xr:uid="{8A330CC4-F2E5-41AF-B02A-B3D83108A029}"/>
+    <hyperlink ref="C59" r:id="rId30" xr:uid="{5FA70CF4-CAEC-44AA-BA96-F6792768C121}"/>
+    <hyperlink ref="C57" r:id="rId31" xr:uid="{D7962EEE-75C0-4E9B-BE8E-B35DE67AD420}"/>
+    <hyperlink ref="C70" r:id="rId32" xr:uid="{4DBF8022-8167-45B5-8197-5DD66D7FBB02}"/>
+    <hyperlink ref="C72" r:id="rId33" xr:uid="{94F10419-84E8-45B6-8A2E-B8EE54E4AA9B}"/>
+    <hyperlink ref="C71" r:id="rId34" xr:uid="{F9D9272F-7F99-468F-902F-F669D1835062}"/>
+    <hyperlink ref="C77" r:id="rId35" xr:uid="{63099BA7-2655-47B9-BE5B-037219A85C72}"/>
+    <hyperlink ref="C79" r:id="rId36" xr:uid="{92B83512-AA12-4644-A63C-9580B6FAB460}"/>
+    <hyperlink ref="C80" r:id="rId37" xr:uid="{C3CF9966-E3D2-47C1-AAF6-020B57E867F9}"/>
+    <hyperlink ref="C83" r:id="rId38" xr:uid="{D8EA092A-34BC-4D08-AC02-BB251B1957BB}"/>
+    <hyperlink ref="C84" r:id="rId39" xr:uid="{F286AF64-A6D8-4AFB-A1E8-F71AD963C030}"/>
+    <hyperlink ref="C68" r:id="rId40" xr:uid="{975EDAE0-C0F5-4E5E-9E92-CFD7EE8FA840}"/>
+    <hyperlink ref="C47" r:id="rId41" xr:uid="{D1A8AAF4-04EE-44C1-909F-83BEA6AD234F}"/>
+    <hyperlink ref="C46" r:id="rId42" xr:uid="{24F7061A-484C-4698-B279-36B2AC2F6704}"/>
+    <hyperlink ref="C45" r:id="rId43" xr:uid="{B482E0B0-395D-4001-AA7D-10472623219D}"/>
+    <hyperlink ref="C44" r:id="rId44" xr:uid="{629AC615-A440-471E-85EF-CFAA30A33ECA}"/>
+    <hyperlink ref="C42" r:id="rId45" xr:uid="{1122AA4B-EE9B-4400-ABDC-433289974BF2}"/>
+    <hyperlink ref="C54" r:id="rId46" xr:uid="{82393856-6D82-40F5-8154-0A46D5D05C97}"/>
+    <hyperlink ref="C53" r:id="rId47" xr:uid="{BDEE30F3-0260-4924-BB76-FAC780D50395}"/>
+    <hyperlink ref="C50" r:id="rId48" xr:uid="{957A3343-4D5E-4F81-91F0-DB46512F3BDB}"/>
+    <hyperlink ref="C39" r:id="rId49" xr:uid="{14E8E0CC-468C-4074-9812-A32568E5B01C}"/>
+    <hyperlink ref="C38" r:id="rId50" xr:uid="{A187B072-87DB-40D2-900A-7B825EB21BBE}"/>
+    <hyperlink ref="C37" r:id="rId51" xr:uid="{11CC2E70-E575-467E-858D-480EA8E52480}"/>
+    <hyperlink ref="C36" r:id="rId52" xr:uid="{A3599C39-5D62-4E34-AA1A-BC60A5D4A0F4}"/>
+    <hyperlink ref="C35" r:id="rId53" xr:uid="{89E041D2-38FD-4318-9D51-EE5E3CD85A2F}"/>
+    <hyperlink ref="C34" r:id="rId54" xr:uid="{2E198E57-AF0E-4553-BF9E-9A36F5287650}"/>
+    <hyperlink ref="C33" r:id="rId55" xr:uid="{207B088B-ECF3-4032-AF0B-3A224D0DEE9B}"/>
+    <hyperlink ref="C11" r:id="rId56" xr:uid="{A3FF1844-52E0-4CBF-8F6E-D2B9904CFA1F}"/>
+    <hyperlink ref="C82" r:id="rId57" xr:uid="{61BBCC75-7C73-4596-95E7-5B192F2B2352}"/>
+    <hyperlink ref="C81" r:id="rId58" xr:uid="{5F534A25-EB0A-4DAD-B575-E9C10C604AE1}"/>
+    <hyperlink ref="C78" r:id="rId59" xr:uid="{A027F9DF-57AD-42B9-ABB9-AD0209F64BE1}"/>
+    <hyperlink ref="C76" r:id="rId60" xr:uid="{31874FA8-D08C-4AE1-87E4-D903C229F3F2}"/>
+    <hyperlink ref="C90" r:id="rId61" xr:uid="{5F714121-DE38-4016-9B13-E9BAF5356525}"/>
+    <hyperlink ref="C67" r:id="rId62" xr:uid="{74241B85-CAA6-4051-9802-D7660DDFB93C}"/>
+    <hyperlink ref="C61" r:id="rId63" xr:uid="{4097DB6A-E976-42AF-9512-D2AEAD9935BF}"/>
+    <hyperlink ref="C52" r:id="rId64" xr:uid="{0D5C1979-4FE7-41F2-8A34-67FEC003B367}"/>
+    <hyperlink ref="C51" r:id="rId65" xr:uid="{065FCE08-DBF9-4B34-AC5D-7C3D5119A871}"/>
+    <hyperlink ref="C49" r:id="rId66" xr:uid="{D6F31E10-EA46-4812-996B-85B8CCC1E4B1}"/>
+    <hyperlink ref="C19" r:id="rId67" xr:uid="{F3E87463-5AA5-4488-A05D-A1B21E197810}"/>
+    <hyperlink ref="C15" r:id="rId68" xr:uid="{84704D3A-5C48-4A62-BE8C-B7586875F536}"/>
+    <hyperlink ref="C17" r:id="rId69" xr:uid="{73891CB5-1A48-4F16-8329-29F01157DB87}"/>
+    <hyperlink ref="C12" r:id="rId70" xr:uid="{84AF008A-C7F6-4AED-AF01-DC5E920EF62D}"/>
+    <hyperlink ref="C10" r:id="rId71" xr:uid="{76395209-2D34-42A1-B04F-2FAF258117A1}"/>
+    <hyperlink ref="C58" r:id="rId72" xr:uid="{07BE94C2-6A3A-4F44-A5FE-0948AFB613EE}"/>
+    <hyperlink ref="C64" r:id="rId73" xr:uid="{BAEB5DCB-83C7-4756-B0F6-FEDDCADBF98E}"/>
+    <hyperlink ref="C66" r:id="rId74" xr:uid="{FB4FA22F-B23E-4E8B-8221-7118631FC71B}"/>
+    <hyperlink ref="C69" r:id="rId75" xr:uid="{A9ED6905-46C6-428C-826B-CD3F8ABAC3D3}"/>
+    <hyperlink ref="C26" r:id="rId76" xr:uid="{14FBA735-FFDC-4054-AF1A-1DB4DBC8FF1D}"/>
+    <hyperlink ref="C14" r:id="rId77" xr:uid="{7C89A834-5498-4A92-928B-FCB42B8E04CB}"/>
+    <hyperlink ref="C5" r:id="rId78" xr:uid="{761D8A75-8DD7-421C-9080-61C17079ECF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
